--- a/BD_productos_nombres_corregidos.xlsx
+++ b/BD_productos_nombres_corregidos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\uriel\OneDrive\Escritorio\MODULAR\MODULAR2\CODE\PrediVent\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenov\OneDrive\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B98A5CB-4ED3-4340-AFB7-44D0DA8E386C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B06B11B-DF9B-4DC8-9F31-1794F7604A25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="16608" windowHeight="8832" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="productos" sheetId="1" r:id="rId1"/>
@@ -20,24 +20,11 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">productos!$A$1:$H$100</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="310">
   <si>
     <t>document_id</t>
   </si>
@@ -682,6 +669,291 @@
   </si>
   <si>
     <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/01%20-%20Laptop%20HP%20Victus%2015.png</t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/03%20-%20Monitor%20Gamer%20ASUS%20TUF%20Gaming%20VG27.png</t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/04%20-%20Teclado%20Gamer%20Redragon%20K552%20Kumara.png</t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/05%20-%20Mouse%20Logitech%20M185.png</t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/06%20-%20Mouse%20Gamer%20Logitech%20G203%20LIGHTSYNC.png</t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/07%20-%20Teclado%20Gamer%20Redragon%20K552%20Kumara.png</t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/08%20-%20Webcam%20Logitech%20C920.png</t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/09%20-%20Microfono%20USB%20FIFINE.png</t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/10%20-%20Bocinas%20USB%20Creative%20Pebble%20V3.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/02%20-%20Computadora%20Todo%20en%20Uno%20Lenovo%20IdeaCentre%20AIO%203.png  </t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/11%20-%20Audifonos%20por%20Cable%20JBL%20Quantum.png</t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/12%20-%20Soporte%20para%20Laptop%20Nexstand%20K2.png</t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/13%20-%20Soporte%20para%20Monitor%20VIVO%20STAND-V001.png</t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/14%20-%20Extensor%20WiFi%20TP-Link%20RE315.png</t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/15%20-%20Adaptador%20USB%20UGREEN%20USB%203.0.png</t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/16%20-%20Memoria%20USB%20SanDisk%20Ultra%20USB%203.0%20(1).png</t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/17%20-%20Tarjeta%20SD%20SanDisk%20Ultra%20SDXC.png</t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/18%20-%20SSD%20Externo%20Kingston%20XS1000.png</t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/19%20-%20HDD%20Externo%20Seagate%20Expansion.png</t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/20%20-%20Cable%20Ethernet%20TP-Link%20Cat%206.png</t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/21%20-%20Memoria%20RAM%20Kingston%20Fury%20Beast%20DDR4.png</t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/22%20-%20Tarjeta%20Grafica%20ASUS%20Dual%20GeForce%20RTX%204060.png</t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/23%20-%20Fuente%20de%20Poder%20Corsair%20CX650.png</t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/24%20-%20Gabinete%20para%20PC%20NZXT%20H5%20(1).png</t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/25%20-%20Ventilador%20para%20PC%20Cooler%20Master%20SickleFlow%20120.png</t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/26%20-%20Celular%20Samsung%20Galaxy%20S24.png</t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/27%20-%20Tablet%20Xiaomi%20Pad%207.png</t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/28%20-%20Smartwatch%20Apple%20Watch%20Series%2010.png</t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/29%20-%20Pulsera%20Inteligente%20Xiaomi%20Smart%20Band%209.png</t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/30%20-%20Cargador%20USB-C%20Anker%20323.png</t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/31%20-%20Cargador%20Inalambrico%20Belkin%20BoostCharge.png</t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/32%20-%20Cable%20USB-C%20UGREEN.png</t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/33%20-%20Cable%20Lightning%20Anker%20PowerLine%20II.png</t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/34%20-%20Cable%20Micro%20USB%20UGREEN.png</t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/35%20-%20Power%20Bank%20Xiaomi%2010000mAh.png</t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/36%20-%20Funda%20para%20iPhone%20Spigen%20Ultra%20Hybrid.png</t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/37%20-%20rotector%20de%20Cristal%20Spigen%20Glas.tR%20EZ%20Fit.png</t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/38%20-%20Soporte%20para%20Celular%20UGREEN%20Foldable.png</t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/39%20-%20Selfie%20Stick%20Xiaomi.png</t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/40%20-%20Lector%20de%20Tarjetas%20UGREEN%20USB%203.0.png</t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/41%20-%20Adaptador%20OTG%20UGREEN%20USB-C.png</t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/42%20-%20Audifonos%20JBL%20buds.png</t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/43%20-%20Aipods%20Pro%20Max.png</t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/44%20-%20Audifonos%20de%20Diadema%20Sony%20WH-CH520.png</t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/45%20-%20Bocina%20JBL%20Charge%205.png</t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/46%20-%20Consola%20PlayStation%205%20Slim.png</t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/47%20-%20Consola%20Xbox%20Series%20X.png</t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/48%20-%20Consola%20Xbox%20Series%20S.png</t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/49%20-%20Consola%20Nintendo%20Switch%20OLED.png</t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/50%20-%20Control%20Gamer%20Sony%20DualSense.png</t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/51%20-%20Control%20Gamer%20Xbox%20Wireless%20Controller.png</t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/52%20-%20Control%20Joy-Con%20Nintendo%20Switch.png</t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/54%20-%20Foco%20LED%20Philips%209W.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/55%20-%20Consola%20Portatil%20ASUS%20ROG%20Ally.png  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/56%20-%20Lenovo%20Legion%20Go.png </t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/57%20-%20camara%20nintendo%20sw.png</t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/58%20-%20Volante%20Gamer%20Logitech%20G29%20Driving%20Force.png</t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/59%20-%20SSD%20M.2%20Kingston%20NV2%20NVMe.png</t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/60%20-%20TV%20TCL%2055P635%204K.png</t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/61%20-%20Google%20Chromecast%20with%20Google%20TV.png</t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/62%20-%20TV%20Box%20Xiaomi%20TV%20Box%20S.png</t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/63%20-%20Roku%20Express%204K.png</t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/64%20-%20Fire%20TV%20Stick%20Amazon%204K%20(1).png</t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/65%20-%20Barra%20de%20Sonido%20Sonos%20Beam.png</t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/66%20-%20Barra%20de%20Sonido%20JBL%20Bar%202.1%20Deep%20Bass.png</t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/67%20-%20Equipo%20de%20Sonido%20Sony%20MHC-V43D.png</t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/68%20-%20Altavoz%20Inteligente%20Amazon%20Echo%20Dot.png</t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/69%20-%20Proyector%204K%20Epson%20EpiqVision%20Mini.png</t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/70%20-%20Reproductor%20Blu-ray%20Sony%20BDP-S1700.png</t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/71%20-%20Camara%20HD%20Sony%20para%20PS5.png</t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/72%20-%20Camara%20Fujifilm%20Instax%20Mini%2012.png</t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/73%20-%20Camara%20Sony%20Alpha%20a6400.png</t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/74%20-%20tripoide.png</t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/75%20-%20Microfono%20Gamer%20HyperX%20QuadCast%20S.png</t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/76%20-%20Router%20WiFi%20TP-Link%20Archer%20AX23.png</t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/77%20-%20Repetidor%20WiFi%20TP-Link%20RE200.png</t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/78%20-Extensor%20WiFi%20TP-Link%20RE550.png</t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/79%20-%20Cable%20HDMI%20UGREEN%202.0.png</t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/80%20-%20Impresora%20Epson%20EcoTank%20L3250.png</t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/81%20-%20Camara%20Wifi.png</t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/82%20-%20Videoportero%20Inteligente%20EZVIZ%20HP7.png</t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/83%20-%20Enchufe%20WiFi%20TP-Link%20Tapo%20P100.png</t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/84%20-%20Control%20Gamer%208BitDo%20Ultimate%20C.png</t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/85%20-%20Cerradura%20Inteligente%20Yale%20Assure%20Lock%202.png</t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/86%20-%20Regulador%20de%20Voltaje%20Koblenz%20RS-1410.png</t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/87%20-%20No-Break%20UPS%20CyberPower%20CP1500AVRLCD.png</t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/88%20-%20Multicontacto%20Koblenz%206%20Contactos.png</t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/90%20-%20Cargador%20de%20baterias.png</t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/91%20-%20Lampara%20LED%20USB%20Baseus.png</t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/92%20-%20Lampara%20LED%20Philips%20Desk%20Lamp.png</t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/94%20-%20Escaner.png</t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/95%20-%20Mini%20Panel%20Solar%20ALLPOWERS.png</t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/96%20-%20Escaner%20Epson%20WorkForce%20ES-50.png</t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/97%20-Calculadora%20cientifica%20cassio.png</t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/98-%20Adaptador%20BT.png</t>
+  </si>
+  <si>
+    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/99%20-%20HDD%20Interno%20Western%20Digital%20Blue.png</t>
   </si>
 </sst>
 </file>
@@ -691,7 +963,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -708,6 +980,14 @@
       <b/>
       <sz val="14"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -732,10 +1012,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -743,8 +1024,10 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1046,7 +1329,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H100"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -1055,11 +1338,11 @@
     <col min="5" max="5" width="14" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="16" customWidth="1"/>
-    <col min="8" max="8" width="75.85546875" customWidth="1"/>
-    <col min="9" max="9" width="30.42578125" customWidth="1"/>
+    <col min="8" max="8" width="75.88671875" customWidth="1"/>
+    <col min="9" max="9" width="30.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1085,7 +1368,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1106,13 +1389,13 @@
       </c>
       <c r="G2" s="2">
         <f t="shared" ref="G2:G33" ca="1" si="0">RANDBETWEEN(1, 10)</f>
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H2" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1133,10 +1416,13 @@
       </c>
       <c r="G3" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1157,10 +1443,13 @@
       </c>
       <c r="G4" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="H4" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1181,10 +1470,13 @@
       </c>
       <c r="G5" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="H5" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1205,10 +1497,13 @@
       </c>
       <c r="G6" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="H6" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1231,8 +1526,11 @@
         <f t="shared" ca="1" si="0"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H7" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1253,10 +1551,13 @@
       </c>
       <c r="G8" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="H8" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1279,8 +1580,11 @@
         <f t="shared" ca="1" si="0"/>
         <v>7</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H9" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1301,10 +1605,13 @@
       </c>
       <c r="G10" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="H10" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1325,10 +1632,13 @@
       </c>
       <c r="G11" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="H11" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1351,8 +1661,11 @@
         <f t="shared" ca="1" si="0"/>
         <v>6</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H12" s="5" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1373,10 +1686,13 @@
       </c>
       <c r="G13" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="H13" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1397,10 +1713,13 @@
       </c>
       <c r="G14" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="H14" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1421,10 +1740,13 @@
       </c>
       <c r="G15" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="H15" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1445,10 +1767,13 @@
       </c>
       <c r="G16" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="H16" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1469,10 +1794,13 @@
       </c>
       <c r="G17" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="H17" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1493,10 +1821,13 @@
       </c>
       <c r="G18" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="H18" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1517,10 +1848,13 @@
       </c>
       <c r="G19" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="H19" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1541,10 +1875,13 @@
       </c>
       <c r="G20" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="H20" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1565,10 +1902,13 @@
       </c>
       <c r="G21" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="H21" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1589,10 +1929,13 @@
       </c>
       <c r="G22" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="H22" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1615,8 +1958,11 @@
         <f t="shared" ca="1" si="0"/>
         <v>9</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H23" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1639,8 +1985,11 @@
         <f t="shared" ca="1" si="0"/>
         <v>8</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H24" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1661,10 +2010,13 @@
       </c>
       <c r="G25" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+      <c r="H25" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1685,10 +2037,13 @@
       </c>
       <c r="G26" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="H26" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
@@ -1709,10 +2064,13 @@
       </c>
       <c r="G27" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="H27" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
@@ -1733,10 +2091,13 @@
       </c>
       <c r="G28" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+      <c r="H28" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
@@ -1757,10 +2118,13 @@
       </c>
       <c r="G29" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="H29" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
@@ -1781,10 +2145,13 @@
       </c>
       <c r="G30" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="H30" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>30</v>
       </c>
@@ -1805,10 +2172,13 @@
       </c>
       <c r="G31" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+      <c r="H31" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>31</v>
       </c>
@@ -1829,10 +2199,13 @@
       </c>
       <c r="G32" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="H32" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>32</v>
       </c>
@@ -1853,10 +2226,13 @@
       </c>
       <c r="G33" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="H33" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>33</v>
       </c>
@@ -1877,10 +2253,13 @@
       </c>
       <c r="G34" s="2">
         <f t="shared" ref="G34:G65" ca="1" si="1">RANDBETWEEN(1, 10)</f>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="H34" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>34</v>
       </c>
@@ -1901,10 +2280,13 @@
       </c>
       <c r="G35" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+      <c r="H35" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>35</v>
       </c>
@@ -1925,10 +2307,13 @@
       </c>
       <c r="G36" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="H36" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>36</v>
       </c>
@@ -1949,10 +2334,13 @@
       </c>
       <c r="G37" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="H37" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>37</v>
       </c>
@@ -1975,8 +2363,11 @@
         <f t="shared" ca="1" si="1"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H38" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>38</v>
       </c>
@@ -1997,10 +2388,13 @@
       </c>
       <c r="G39" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+      <c r="H39" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>39</v>
       </c>
@@ -2021,10 +2415,13 @@
       </c>
       <c r="G40" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+      <c r="H40" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>40</v>
       </c>
@@ -2045,10 +2442,13 @@
       </c>
       <c r="G41" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+      <c r="H41" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>41</v>
       </c>
@@ -2069,10 +2469,13 @@
       </c>
       <c r="G42" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="H42" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>42</v>
       </c>
@@ -2093,10 +2496,13 @@
       </c>
       <c r="G43" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="H43" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>43</v>
       </c>
@@ -2117,10 +2523,13 @@
       </c>
       <c r="G44" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="H44" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>44</v>
       </c>
@@ -2141,10 +2550,13 @@
       </c>
       <c r="G45" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="H45" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>45</v>
       </c>
@@ -2165,10 +2577,13 @@
       </c>
       <c r="G46" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+      <c r="H46" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>46</v>
       </c>
@@ -2189,10 +2604,13 @@
       </c>
       <c r="G47" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+      <c r="H47" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>47</v>
       </c>
@@ -2213,10 +2631,13 @@
       </c>
       <c r="G48" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="H48" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>48</v>
       </c>
@@ -2237,10 +2658,13 @@
       </c>
       <c r="G49" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="H49" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>49</v>
       </c>
@@ -2261,10 +2685,13 @@
       </c>
       <c r="G50" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="H50" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>50</v>
       </c>
@@ -2285,10 +2712,13 @@
       </c>
       <c r="G51" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="H51" s="5" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>51</v>
       </c>
@@ -2309,10 +2739,13 @@
       </c>
       <c r="G52" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="H52" s="5" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>52</v>
       </c>
@@ -2333,10 +2766,13 @@
       </c>
       <c r="G53" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="H53" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>53</v>
       </c>
@@ -2357,10 +2793,13 @@
       </c>
       <c r="G54" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="H54" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>54</v>
       </c>
@@ -2383,8 +2822,11 @@
         <f t="shared" ca="1" si="1"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H55" s="5" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>55</v>
       </c>
@@ -2407,8 +2849,11 @@
         <f t="shared" ca="1" si="1"/>
         <v>4</v>
       </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H56" s="5" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>56</v>
       </c>
@@ -2429,10 +2874,13 @@
       </c>
       <c r="G57" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="H57" s="5" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>57</v>
       </c>
@@ -2455,8 +2903,11 @@
         <f t="shared" ca="1" si="1"/>
         <v>8</v>
       </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H58" s="5" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>58</v>
       </c>
@@ -2477,10 +2928,13 @@
       </c>
       <c r="G59" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="H59" s="5" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>59</v>
       </c>
@@ -2501,10 +2955,13 @@
       </c>
       <c r="G60" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="H60" s="5" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>60</v>
       </c>
@@ -2524,11 +2981,14 @@
         <v>3</v>
       </c>
       <c r="G61" s="2">
-        <f t="shared" ca="1" si="1"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+        <f ca="1">RANDBETWEEN(1, 10)</f>
+        <v>4</v>
+      </c>
+      <c r="H61" s="5" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>61</v>
       </c>
@@ -2551,8 +3011,11 @@
         <f t="shared" ca="1" si="1"/>
         <v>6</v>
       </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H62" s="5" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>62</v>
       </c>
@@ -2573,10 +3036,13 @@
       </c>
       <c r="G63" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="H63" s="5" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>63</v>
       </c>
@@ -2597,10 +3063,13 @@
       </c>
       <c r="G64" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="H64" s="5" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>64</v>
       </c>
@@ -2621,10 +3090,13 @@
       </c>
       <c r="G65" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="H65" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>65</v>
       </c>
@@ -2645,10 +3117,13 @@
       </c>
       <c r="G66" s="2">
         <f t="shared" ref="G66:G100" ca="1" si="2">RANDBETWEEN(1, 10)</f>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+      <c r="H66" s="5" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>66</v>
       </c>
@@ -2669,10 +3144,13 @@
       </c>
       <c r="G67" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="H67" s="5" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>67</v>
       </c>
@@ -2693,10 +3171,13 @@
       </c>
       <c r="G68" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="H68" s="5" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>68</v>
       </c>
@@ -2717,10 +3198,13 @@
       </c>
       <c r="G69" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="H69" s="5" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>69</v>
       </c>
@@ -2741,10 +3225,13 @@
       </c>
       <c r="G70" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="H70" s="5" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>70</v>
       </c>
@@ -2767,8 +3254,11 @@
         <f t="shared" ca="1" si="2"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H71" s="5" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>71</v>
       </c>
@@ -2789,10 +3279,13 @@
       </c>
       <c r="G72" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="H72" s="5" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>72</v>
       </c>
@@ -2813,10 +3306,13 @@
       </c>
       <c r="G73" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="H73" s="5" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>73</v>
       </c>
@@ -2837,10 +3333,13 @@
       </c>
       <c r="G74" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="H74" s="5" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>74</v>
       </c>
@@ -2861,10 +3360,13 @@
       </c>
       <c r="G75" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+      <c r="H75" s="5" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>75</v>
       </c>
@@ -2885,10 +3387,13 @@
       </c>
       <c r="G76" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="H76" s="5" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>76</v>
       </c>
@@ -2909,10 +3414,13 @@
       </c>
       <c r="G77" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="H77" s="5" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>77</v>
       </c>
@@ -2933,10 +3441,13 @@
       </c>
       <c r="G78" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="H78" s="5" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>78</v>
       </c>
@@ -2957,10 +3468,13 @@
       </c>
       <c r="G79" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+      <c r="H79" s="5" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>79</v>
       </c>
@@ -2981,10 +3495,13 @@
       </c>
       <c r="G80" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="H80" s="5" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>80</v>
       </c>
@@ -3005,10 +3522,13 @@
       </c>
       <c r="G81" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="H81" s="5" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>81</v>
       </c>
@@ -3029,10 +3549,13 @@
       </c>
       <c r="G82" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="H82" s="5" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>82</v>
       </c>
@@ -3053,10 +3576,13 @@
       </c>
       <c r="G83" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+      <c r="H83" s="5" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>83</v>
       </c>
@@ -3077,10 +3603,13 @@
       </c>
       <c r="G84" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="H84" s="5" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>84</v>
       </c>
@@ -3101,10 +3630,13 @@
       </c>
       <c r="G85" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+      <c r="H85" s="5" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>85</v>
       </c>
@@ -3125,10 +3657,13 @@
       </c>
       <c r="G86" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="H86" s="5" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>86</v>
       </c>
@@ -3149,10 +3684,13 @@
       </c>
       <c r="G87" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="H87" s="5" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>87</v>
       </c>
@@ -3173,10 +3711,13 @@
       </c>
       <c r="G88" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="H88" s="5" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>88</v>
       </c>
@@ -3197,10 +3738,13 @@
       </c>
       <c r="G89" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="H89" s="5" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>89</v>
       </c>
@@ -3221,10 +3765,13 @@
       </c>
       <c r="G90" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="H90" s="5" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>90</v>
       </c>
@@ -3245,10 +3792,13 @@
       </c>
       <c r="G91" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="H91" s="5" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>91</v>
       </c>
@@ -3269,10 +3819,13 @@
       </c>
       <c r="G92" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="H92" s="5" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>92</v>
       </c>
@@ -3293,10 +3846,13 @@
       </c>
       <c r="G93" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="H93" s="5" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>93</v>
       </c>
@@ -3317,10 +3873,13 @@
       </c>
       <c r="G94" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+      <c r="H94" s="5" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>94</v>
       </c>
@@ -3341,10 +3900,13 @@
       </c>
       <c r="G95" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="H95" s="5" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>95</v>
       </c>
@@ -3365,10 +3927,13 @@
       </c>
       <c r="G96" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="H96" s="5" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>96</v>
       </c>
@@ -3389,10 +3954,13 @@
       </c>
       <c r="G97" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="H97" s="5" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>97</v>
       </c>
@@ -3413,10 +3981,13 @@
       </c>
       <c r="G98" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="H98" s="5" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>98</v>
       </c>
@@ -3437,10 +4008,13 @@
       </c>
       <c r="G99" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+      <c r="H99" s="5" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>99</v>
       </c>
@@ -3461,11 +4035,65 @@
       </c>
       <c r="G100" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="H100" s="5" t="s">
+        <v>309</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:H100" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <hyperlinks>
+    <hyperlink ref="H3" r:id="rId1" xr:uid="{44740A5E-F109-45C6-9A13-A4F4EAE7DA81}"/>
+    <hyperlink ref="H12" r:id="rId2" xr:uid="{5E504EC7-8957-471C-B719-01B4D83517D1}"/>
+    <hyperlink ref="H51" r:id="rId3" xr:uid="{5CC7E1F3-04A5-4009-A7F4-5ECB1A994925}"/>
+    <hyperlink ref="H52" r:id="rId4" xr:uid="{C1A25437-EB6E-40A0-B5E5-96CD29804ED2}"/>
+    <hyperlink ref="H55" r:id="rId5" xr:uid="{C82D2E6E-5B24-44A4-BB1D-BB7211C1C852}"/>
+    <hyperlink ref="H56" r:id="rId6" xr:uid="{A776E588-BCB3-42B5-9B8B-6B48E80A853A}"/>
+    <hyperlink ref="H57" r:id="rId7" xr:uid="{33844AF3-3EEE-4941-B5EF-167FF332493C}"/>
+    <hyperlink ref="H58" r:id="rId8" xr:uid="{2FD1BD28-5F5B-4289-B314-E2BB5E951180}"/>
+    <hyperlink ref="H59" r:id="rId9" xr:uid="{0CDB450D-4511-4658-9489-ABCC10CEB849}"/>
+    <hyperlink ref="H60" r:id="rId10" xr:uid="{88107DD1-E3ED-4421-BED5-3435BABCC4C4}"/>
+    <hyperlink ref="H61" r:id="rId11" xr:uid="{1A0DBDE6-E104-4A64-BB18-E4AF78B5EB84}"/>
+    <hyperlink ref="H62" r:id="rId12" xr:uid="{4932B75A-12AD-4804-BCC0-7B9EB836719E}"/>
+    <hyperlink ref="H63" r:id="rId13" xr:uid="{1C257451-3AE9-4C62-B004-979BCAF136A5}"/>
+    <hyperlink ref="H64" r:id="rId14" xr:uid="{2673EB38-A1B0-4C75-A957-F5E04BCAB107}"/>
+    <hyperlink ref="H66" r:id="rId15" xr:uid="{7093BCDF-6508-4C60-B589-52963C6F310F}"/>
+    <hyperlink ref="H67" r:id="rId16" xr:uid="{3ED3150C-C5B5-441E-B63F-40E5D95E65B2}"/>
+    <hyperlink ref="H68" r:id="rId17" xr:uid="{7B6D0D5E-7368-476A-826F-E7039336A52B}"/>
+    <hyperlink ref="H69" r:id="rId18" xr:uid="{43D3C846-AE63-481A-ABB3-847A96CC03E5}"/>
+    <hyperlink ref="H70" r:id="rId19" xr:uid="{8783941C-25FE-419E-A3E7-3DFD5F3096FE}"/>
+    <hyperlink ref="H71" r:id="rId20" xr:uid="{98860619-505F-452F-9D2B-8BCE693D3685}"/>
+    <hyperlink ref="H72" r:id="rId21" xr:uid="{A38E2513-94D0-4F9B-A4FB-D05A2D01FED9}"/>
+    <hyperlink ref="H73" r:id="rId22" xr:uid="{40C96FF8-5B4E-4AD6-8EE6-0B558951F95F}"/>
+    <hyperlink ref="H74" r:id="rId23" xr:uid="{FB7D81B4-E308-4530-A633-581C3F2A2B8A}"/>
+    <hyperlink ref="H75" r:id="rId24" xr:uid="{71FCCE82-76BF-4E43-B3CB-B1A4B928EB8C}"/>
+    <hyperlink ref="H76" r:id="rId25" xr:uid="{0D33E3C9-200F-46A0-AFA8-54FB5B2EB73B}"/>
+    <hyperlink ref="H77" r:id="rId26" xr:uid="{A989841E-1A9E-4269-94BF-15036737062B}"/>
+    <hyperlink ref="H78" r:id="rId27" xr:uid="{8CCCC026-66DF-449C-93BE-B04BD3B91F6A}"/>
+    <hyperlink ref="H79" r:id="rId28" xr:uid="{8DBA4129-2CF4-4D14-9A86-708A9F563C54}"/>
+    <hyperlink ref="H80" r:id="rId29" xr:uid="{6DF75FA9-FB4A-44D0-842E-AC1BFEDF945E}"/>
+    <hyperlink ref="H81" r:id="rId30" xr:uid="{8FF9D50D-1EBE-4B7A-B71D-DE5197A3D058}"/>
+    <hyperlink ref="H82" r:id="rId31" xr:uid="{4AF5ABF4-34B3-4D4B-A799-C1F581D732DE}"/>
+    <hyperlink ref="H83" r:id="rId32" xr:uid="{BCDAA5FF-A5EF-455D-99D7-857F9FC47BAC}"/>
+    <hyperlink ref="H84" r:id="rId33" xr:uid="{95B77834-26FC-480C-9360-A25B94900AAB}"/>
+    <hyperlink ref="H85" r:id="rId34" xr:uid="{B822F5B5-C946-49A7-A163-1BF19AEB2AD6}"/>
+    <hyperlink ref="H86" r:id="rId35" xr:uid="{0AA68751-4B4F-4D68-A717-9D61EF3D82A7}"/>
+    <hyperlink ref="H87" r:id="rId36" xr:uid="{525CB9BB-42D3-4793-B34F-F0BEC92AC036}"/>
+    <hyperlink ref="H88" r:id="rId37" xr:uid="{24256CC9-4A82-4F7B-AE2D-EBEDD37889C3}"/>
+    <hyperlink ref="H89" r:id="rId38" xr:uid="{5BF35E34-8A05-414F-96C6-BF2775729EFD}"/>
+    <hyperlink ref="H90" r:id="rId39" xr:uid="{12FEED72-670E-468E-9D4F-256CD207E865}"/>
+    <hyperlink ref="H91" r:id="rId40" xr:uid="{8301AD6B-3951-45B1-9DBA-E117868765B9}"/>
+    <hyperlink ref="H92" r:id="rId41" xr:uid="{4C219831-926F-4DE7-9B56-8D15BF54B3AA}"/>
+    <hyperlink ref="H93" r:id="rId42" xr:uid="{B7302327-1130-4B9B-8756-373DC8936B66}"/>
+    <hyperlink ref="H94" r:id="rId43" xr:uid="{BBA880CF-4CB7-4531-A2C9-F68C4D7883BA}"/>
+    <hyperlink ref="H95" r:id="rId44" xr:uid="{E355C69C-6307-4A27-8B56-F5954A79AB80}"/>
+    <hyperlink ref="H96" r:id="rId45" xr:uid="{AD5FDA0E-805E-49C9-9188-6C580E801C60}"/>
+    <hyperlink ref="H97" r:id="rId46" xr:uid="{577F2FF5-1382-452F-966A-995CAA314AC6}"/>
+    <hyperlink ref="H98" r:id="rId47" xr:uid="{353D9869-BF30-464A-BB15-AE91BB3C0ADE}"/>
+    <hyperlink ref="H99" r:id="rId48" xr:uid="{1A419798-3B9C-40CE-B1FB-78B4D81645CB}"/>
+    <hyperlink ref="H100" r:id="rId49" xr:uid="{447A01E2-C841-4209-9A93-78BAA26C2344}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3473,57 +4101,57 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="110" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>213</v>
       </c>

--- a/BD_productos_nombres_corregidos.xlsx
+++ b/BD_productos_nombres_corregidos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenov\OneDrive\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\uriel\OneDrive\Escritorio\MODULAR\MODULAR2\CODE\PrediVent\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B06B11B-DF9B-4DC8-9F31-1794F7604A25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B98A5CB-4ED3-4340-AFB7-44D0DA8E386C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="16608" windowHeight="8832" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="productos" sheetId="1" r:id="rId1"/>
@@ -20,11 +20,24 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">productos!$A$1:$H$100</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="215">
   <si>
     <t>document_id</t>
   </si>
@@ -669,291 +682,6 @@
   </si>
   <si>
     <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/01%20-%20Laptop%20HP%20Victus%2015.png</t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/03%20-%20Monitor%20Gamer%20ASUS%20TUF%20Gaming%20VG27.png</t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/04%20-%20Teclado%20Gamer%20Redragon%20K552%20Kumara.png</t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/05%20-%20Mouse%20Logitech%20M185.png</t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/06%20-%20Mouse%20Gamer%20Logitech%20G203%20LIGHTSYNC.png</t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/07%20-%20Teclado%20Gamer%20Redragon%20K552%20Kumara.png</t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/08%20-%20Webcam%20Logitech%20C920.png</t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/09%20-%20Microfono%20USB%20FIFINE.png</t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/10%20-%20Bocinas%20USB%20Creative%20Pebble%20V3.png</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/02%20-%20Computadora%20Todo%20en%20Uno%20Lenovo%20IdeaCentre%20AIO%203.png  </t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/11%20-%20Audifonos%20por%20Cable%20JBL%20Quantum.png</t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/12%20-%20Soporte%20para%20Laptop%20Nexstand%20K2.png</t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/13%20-%20Soporte%20para%20Monitor%20VIVO%20STAND-V001.png</t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/14%20-%20Extensor%20WiFi%20TP-Link%20RE315.png</t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/15%20-%20Adaptador%20USB%20UGREEN%20USB%203.0.png</t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/16%20-%20Memoria%20USB%20SanDisk%20Ultra%20USB%203.0%20(1).png</t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/17%20-%20Tarjeta%20SD%20SanDisk%20Ultra%20SDXC.png</t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/18%20-%20SSD%20Externo%20Kingston%20XS1000.png</t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/19%20-%20HDD%20Externo%20Seagate%20Expansion.png</t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/20%20-%20Cable%20Ethernet%20TP-Link%20Cat%206.png</t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/21%20-%20Memoria%20RAM%20Kingston%20Fury%20Beast%20DDR4.png</t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/22%20-%20Tarjeta%20Grafica%20ASUS%20Dual%20GeForce%20RTX%204060.png</t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/23%20-%20Fuente%20de%20Poder%20Corsair%20CX650.png</t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/24%20-%20Gabinete%20para%20PC%20NZXT%20H5%20(1).png</t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/25%20-%20Ventilador%20para%20PC%20Cooler%20Master%20SickleFlow%20120.png</t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/26%20-%20Celular%20Samsung%20Galaxy%20S24.png</t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/27%20-%20Tablet%20Xiaomi%20Pad%207.png</t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/28%20-%20Smartwatch%20Apple%20Watch%20Series%2010.png</t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/29%20-%20Pulsera%20Inteligente%20Xiaomi%20Smart%20Band%209.png</t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/30%20-%20Cargador%20USB-C%20Anker%20323.png</t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/31%20-%20Cargador%20Inalambrico%20Belkin%20BoostCharge.png</t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/32%20-%20Cable%20USB-C%20UGREEN.png</t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/33%20-%20Cable%20Lightning%20Anker%20PowerLine%20II.png</t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/34%20-%20Cable%20Micro%20USB%20UGREEN.png</t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/35%20-%20Power%20Bank%20Xiaomi%2010000mAh.png</t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/36%20-%20Funda%20para%20iPhone%20Spigen%20Ultra%20Hybrid.png</t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/37%20-%20rotector%20de%20Cristal%20Spigen%20Glas.tR%20EZ%20Fit.png</t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/38%20-%20Soporte%20para%20Celular%20UGREEN%20Foldable.png</t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/39%20-%20Selfie%20Stick%20Xiaomi.png</t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/40%20-%20Lector%20de%20Tarjetas%20UGREEN%20USB%203.0.png</t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/41%20-%20Adaptador%20OTG%20UGREEN%20USB-C.png</t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/42%20-%20Audifonos%20JBL%20buds.png</t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/43%20-%20Aipods%20Pro%20Max.png</t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/44%20-%20Audifonos%20de%20Diadema%20Sony%20WH-CH520.png</t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/45%20-%20Bocina%20JBL%20Charge%205.png</t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/46%20-%20Consola%20PlayStation%205%20Slim.png</t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/47%20-%20Consola%20Xbox%20Series%20X.png</t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/48%20-%20Consola%20Xbox%20Series%20S.png</t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/49%20-%20Consola%20Nintendo%20Switch%20OLED.png</t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/50%20-%20Control%20Gamer%20Sony%20DualSense.png</t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/51%20-%20Control%20Gamer%20Xbox%20Wireless%20Controller.png</t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/52%20-%20Control%20Joy-Con%20Nintendo%20Switch.png</t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/54%20-%20Foco%20LED%20Philips%209W.png</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/55%20-%20Consola%20Portatil%20ASUS%20ROG%20Ally.png  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/56%20-%20Lenovo%20Legion%20Go.png </t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/57%20-%20camara%20nintendo%20sw.png</t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/58%20-%20Volante%20Gamer%20Logitech%20G29%20Driving%20Force.png</t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/59%20-%20SSD%20M.2%20Kingston%20NV2%20NVMe.png</t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/60%20-%20TV%20TCL%2055P635%204K.png</t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/61%20-%20Google%20Chromecast%20with%20Google%20TV.png</t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/62%20-%20TV%20Box%20Xiaomi%20TV%20Box%20S.png</t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/63%20-%20Roku%20Express%204K.png</t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/64%20-%20Fire%20TV%20Stick%20Amazon%204K%20(1).png</t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/65%20-%20Barra%20de%20Sonido%20Sonos%20Beam.png</t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/66%20-%20Barra%20de%20Sonido%20JBL%20Bar%202.1%20Deep%20Bass.png</t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/67%20-%20Equipo%20de%20Sonido%20Sony%20MHC-V43D.png</t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/68%20-%20Altavoz%20Inteligente%20Amazon%20Echo%20Dot.png</t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/69%20-%20Proyector%204K%20Epson%20EpiqVision%20Mini.png</t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/70%20-%20Reproductor%20Blu-ray%20Sony%20BDP-S1700.png</t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/71%20-%20Camara%20HD%20Sony%20para%20PS5.png</t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/72%20-%20Camara%20Fujifilm%20Instax%20Mini%2012.png</t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/73%20-%20Camara%20Sony%20Alpha%20a6400.png</t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/74%20-%20tripoide.png</t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/75%20-%20Microfono%20Gamer%20HyperX%20QuadCast%20S.png</t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/76%20-%20Router%20WiFi%20TP-Link%20Archer%20AX23.png</t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/77%20-%20Repetidor%20WiFi%20TP-Link%20RE200.png</t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/78%20-Extensor%20WiFi%20TP-Link%20RE550.png</t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/79%20-%20Cable%20HDMI%20UGREEN%202.0.png</t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/80%20-%20Impresora%20Epson%20EcoTank%20L3250.png</t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/81%20-%20Camara%20Wifi.png</t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/82%20-%20Videoportero%20Inteligente%20EZVIZ%20HP7.png</t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/83%20-%20Enchufe%20WiFi%20TP-Link%20Tapo%20P100.png</t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/84%20-%20Control%20Gamer%208BitDo%20Ultimate%20C.png</t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/85%20-%20Cerradura%20Inteligente%20Yale%20Assure%20Lock%202.png</t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/86%20-%20Regulador%20de%20Voltaje%20Koblenz%20RS-1410.png</t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/87%20-%20No-Break%20UPS%20CyberPower%20CP1500AVRLCD.png</t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/88%20-%20Multicontacto%20Koblenz%206%20Contactos.png</t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/90%20-%20Cargador%20de%20baterias.png</t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/91%20-%20Lampara%20LED%20USB%20Baseus.png</t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/92%20-%20Lampara%20LED%20Philips%20Desk%20Lamp.png</t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/94%20-%20Escaner.png</t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/95%20-%20Mini%20Panel%20Solar%20ALLPOWERS.png</t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/96%20-%20Escaner%20Epson%20WorkForce%20ES-50.png</t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/97%20-Calculadora%20cientifica%20cassio.png</t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/98-%20Adaptador%20BT.png</t>
-  </si>
-  <si>
-    <t>https://zjttsdcnlxhzlcacborl.supabase.co/storage/v1/object/public/productos/Imagenes/99%20-%20HDD%20Interno%20Western%20Digital%20Blue.png</t>
   </si>
 </sst>
 </file>
@@ -963,7 +691,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -980,14 +708,6 @@
       <b/>
       <sz val="14"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1012,11 +732,10 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1024,10 +743,8 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1329,7 +1046,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H100"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -1338,11 +1055,11 @@
     <col min="5" max="5" width="14" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="16" customWidth="1"/>
-    <col min="8" max="8" width="75.88671875" customWidth="1"/>
-    <col min="9" max="9" width="30.44140625" customWidth="1"/>
+    <col min="8" max="8" width="75.85546875" customWidth="1"/>
+    <col min="9" max="9" width="30.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1368,7 +1085,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1389,13 +1106,13 @@
       </c>
       <c r="G2" s="2">
         <f t="shared" ref="G2:G33" ca="1" si="0">RANDBETWEEN(1, 10)</f>
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H2" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1416,13 +1133,10 @@
       </c>
       <c r="G3" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1443,13 +1157,10 @@
       </c>
       <c r="G4" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="H4" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1470,13 +1181,10 @@
       </c>
       <c r="G5" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="H5" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1497,13 +1205,10 @@
       </c>
       <c r="G6" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="H6" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1526,11 +1231,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>2</v>
       </c>
-      <c r="H7" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1551,13 +1253,10 @@
       </c>
       <c r="G8" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="H8" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1580,11 +1279,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>7</v>
       </c>
-      <c r="H9" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1605,13 +1301,10 @@
       </c>
       <c r="G10" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="H10" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1632,13 +1325,10 @@
       </c>
       <c r="G11" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="H11" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1661,11 +1351,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>6</v>
       </c>
-      <c r="H12" s="5" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1686,13 +1373,10 @@
       </c>
       <c r="G13" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="H13" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1713,13 +1397,10 @@
       </c>
       <c r="G14" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="H14" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1740,13 +1421,10 @@
       </c>
       <c r="G15" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="H15" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1767,13 +1445,10 @@
       </c>
       <c r="G16" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H16" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1794,13 +1469,10 @@
       </c>
       <c r="G17" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="H17" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1821,13 +1493,10 @@
       </c>
       <c r="G18" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="H18" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1848,13 +1517,10 @@
       </c>
       <c r="G19" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="H19" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1875,13 +1541,10 @@
       </c>
       <c r="G20" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="H20" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1902,13 +1565,10 @@
       </c>
       <c r="G21" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="H21" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1929,13 +1589,10 @@
       </c>
       <c r="G22" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H22" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1958,11 +1615,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>9</v>
       </c>
-      <c r="H23" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1985,11 +1639,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>8</v>
       </c>
-      <c r="H24" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -2010,13 +1661,10 @@
       </c>
       <c r="G25" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="H25" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -2037,13 +1685,10 @@
       </c>
       <c r="G26" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="H26" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -2064,13 +1709,10 @@
       </c>
       <c r="G27" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="H27" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
@@ -2091,13 +1733,10 @@
       </c>
       <c r="G28" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="H28" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -2118,13 +1757,10 @@
       </c>
       <c r="G29" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="H29" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -2145,13 +1781,10 @@
       </c>
       <c r="G30" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="H30" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -2172,13 +1805,10 @@
       </c>
       <c r="G31" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="H31" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
@@ -2199,13 +1829,10 @@
       </c>
       <c r="G32" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="H32" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
@@ -2226,13 +1853,10 @@
       </c>
       <c r="G33" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="H33" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
@@ -2253,13 +1877,10 @@
       </c>
       <c r="G34" s="2">
         <f t="shared" ref="G34:G65" ca="1" si="1">RANDBETWEEN(1, 10)</f>
-        <v>2</v>
-      </c>
-      <c r="H34" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
@@ -2280,13 +1901,10 @@
       </c>
       <c r="G35" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="H35" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
@@ -2307,13 +1925,10 @@
       </c>
       <c r="G36" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="H36" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
@@ -2334,13 +1949,10 @@
       </c>
       <c r="G37" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="H37" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
@@ -2363,11 +1975,8 @@
         <f t="shared" ca="1" si="1"/>
         <v>1</v>
       </c>
-      <c r="H38" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
@@ -2388,13 +1997,10 @@
       </c>
       <c r="G39" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="H39" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
@@ -2415,13 +2021,10 @@
       </c>
       <c r="G40" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="H40" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
@@ -2442,13 +2045,10 @@
       </c>
       <c r="G41" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="H41" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
@@ -2469,13 +2069,10 @@
       </c>
       <c r="G42" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="H42" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
@@ -2496,13 +2093,10 @@
       </c>
       <c r="G43" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>8</v>
-      </c>
-      <c r="H43" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
@@ -2523,13 +2117,10 @@
       </c>
       <c r="G44" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="H44" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
@@ -2550,13 +2141,10 @@
       </c>
       <c r="G45" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="H45" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
@@ -2577,13 +2165,10 @@
       </c>
       <c r="G46" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="H46" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
@@ -2604,13 +2189,10 @@
       </c>
       <c r="G47" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="H47" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
@@ -2631,13 +2213,10 @@
       </c>
       <c r="G48" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="H48" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
@@ -2658,13 +2237,10 @@
       </c>
       <c r="G49" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="H49" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
@@ -2685,13 +2261,10 @@
       </c>
       <c r="G50" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="H50" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>50</v>
       </c>
@@ -2712,13 +2285,10 @@
       </c>
       <c r="G51" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="H51" s="5" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>51</v>
       </c>
@@ -2739,13 +2309,10 @@
       </c>
       <c r="G52" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="H52" s="5" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>52</v>
       </c>
@@ -2766,13 +2333,10 @@
       </c>
       <c r="G53" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="H53" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>53</v>
       </c>
@@ -2793,13 +2357,10 @@
       </c>
       <c r="G54" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="H54" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>54</v>
       </c>
@@ -2822,11 +2383,8 @@
         <f t="shared" ca="1" si="1"/>
         <v>1</v>
       </c>
-      <c r="H55" s="5" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>55</v>
       </c>
@@ -2849,11 +2407,8 @@
         <f t="shared" ca="1" si="1"/>
         <v>4</v>
       </c>
-      <c r="H56" s="5" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>56</v>
       </c>
@@ -2874,13 +2429,10 @@
       </c>
       <c r="G57" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>7</v>
-      </c>
-      <c r="H57" s="5" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>57</v>
       </c>
@@ -2903,11 +2455,8 @@
         <f t="shared" ca="1" si="1"/>
         <v>8</v>
       </c>
-      <c r="H58" s="5" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>58</v>
       </c>
@@ -2928,13 +2477,10 @@
       </c>
       <c r="G59" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="H59" s="5" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>59</v>
       </c>
@@ -2955,13 +2501,10 @@
       </c>
       <c r="G60" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="H60" s="5" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>60</v>
       </c>
@@ -2981,14 +2524,11 @@
         <v>3</v>
       </c>
       <c r="G61" s="2">
-        <f ca="1">RANDBETWEEN(1, 10)</f>
-        <v>4</v>
-      </c>
-      <c r="H61" s="5" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+        <f t="shared" ca="1" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>61</v>
       </c>
@@ -3011,11 +2551,8 @@
         <f t="shared" ca="1" si="1"/>
         <v>6</v>
       </c>
-      <c r="H62" s="5" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>62</v>
       </c>
@@ -3036,13 +2573,10 @@
       </c>
       <c r="G63" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>8</v>
-      </c>
-      <c r="H63" s="5" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>63</v>
       </c>
@@ -3063,13 +2597,10 @@
       </c>
       <c r="G64" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="H64" s="5" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>64</v>
       </c>
@@ -3090,13 +2621,10 @@
       </c>
       <c r="G65" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="H65" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>65</v>
       </c>
@@ -3117,13 +2645,10 @@
       </c>
       <c r="G66" s="2">
         <f t="shared" ref="G66:G100" ca="1" si="2">RANDBETWEEN(1, 10)</f>
-        <v>5</v>
-      </c>
-      <c r="H66" s="5" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>66</v>
       </c>
@@ -3144,13 +2669,10 @@
       </c>
       <c r="G67" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>10</v>
-      </c>
-      <c r="H67" s="5" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>67</v>
       </c>
@@ -3171,13 +2693,10 @@
       </c>
       <c r="G68" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>8</v>
-      </c>
-      <c r="H68" s="5" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>68</v>
       </c>
@@ -3198,13 +2717,10 @@
       </c>
       <c r="G69" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>7</v>
-      </c>
-      <c r="H69" s="5" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>69</v>
       </c>
@@ -3225,13 +2741,10 @@
       </c>
       <c r="G70" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
-      </c>
-      <c r="H70" s="5" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>70</v>
       </c>
@@ -3254,11 +2767,8 @@
         <f t="shared" ca="1" si="2"/>
         <v>1</v>
       </c>
-      <c r="H71" s="5" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>71</v>
       </c>
@@ -3279,13 +2789,10 @@
       </c>
       <c r="G72" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>7</v>
-      </c>
-      <c r="H72" s="5" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>72</v>
       </c>
@@ -3306,13 +2813,10 @@
       </c>
       <c r="G73" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
-      </c>
-      <c r="H73" s="5" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>73</v>
       </c>
@@ -3333,13 +2837,10 @@
       </c>
       <c r="G74" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="H74" s="5" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>74</v>
       </c>
@@ -3360,13 +2861,10 @@
       </c>
       <c r="G75" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
-      </c>
-      <c r="H75" s="5" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>75</v>
       </c>
@@ -3387,13 +2885,10 @@
       </c>
       <c r="G76" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>6</v>
-      </c>
-      <c r="H76" s="5" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>76</v>
       </c>
@@ -3414,13 +2909,10 @@
       </c>
       <c r="G77" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>10</v>
-      </c>
-      <c r="H77" s="5" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>77</v>
       </c>
@@ -3441,13 +2933,10 @@
       </c>
       <c r="G78" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
-      </c>
-      <c r="H78" s="5" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>78</v>
       </c>
@@ -3468,13 +2957,10 @@
       </c>
       <c r="G79" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
-      </c>
-      <c r="H79" s="5" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>79</v>
       </c>
@@ -3495,13 +2981,10 @@
       </c>
       <c r="G80" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="H80" s="5" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>80</v>
       </c>
@@ -3522,13 +3005,10 @@
       </c>
       <c r="G81" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>7</v>
-      </c>
-      <c r="H81" s="5" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>81</v>
       </c>
@@ -3549,13 +3029,10 @@
       </c>
       <c r="G82" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="H82" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>82</v>
       </c>
@@ -3576,13 +3053,10 @@
       </c>
       <c r="G83" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>9</v>
-      </c>
-      <c r="H83" s="5" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>83</v>
       </c>
@@ -3603,13 +3077,10 @@
       </c>
       <c r="G84" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="H84" s="5" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>84</v>
       </c>
@@ -3630,13 +3101,10 @@
       </c>
       <c r="G85" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
-      </c>
-      <c r="H85" s="5" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>85</v>
       </c>
@@ -3657,13 +3125,10 @@
       </c>
       <c r="G86" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>10</v>
-      </c>
-      <c r="H86" s="5" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>86</v>
       </c>
@@ -3684,13 +3149,10 @@
       </c>
       <c r="G87" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="H87" s="5" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>87</v>
       </c>
@@ -3711,13 +3173,10 @@
       </c>
       <c r="G88" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="H88" s="5" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>88</v>
       </c>
@@ -3738,13 +3197,10 @@
       </c>
       <c r="G89" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="H89" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>89</v>
       </c>
@@ -3765,13 +3221,10 @@
       </c>
       <c r="G90" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
-      </c>
-      <c r="H90" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>90</v>
       </c>
@@ -3792,13 +3245,10 @@
       </c>
       <c r="G91" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>10</v>
-      </c>
-      <c r="H91" s="5" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>91</v>
       </c>
@@ -3819,13 +3269,10 @@
       </c>
       <c r="G92" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>7</v>
-      </c>
-      <c r="H92" s="5" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>92</v>
       </c>
@@ -3846,13 +3293,10 @@
       </c>
       <c r="G93" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>10</v>
-      </c>
-      <c r="H93" s="5" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>93</v>
       </c>
@@ -3873,13 +3317,10 @@
       </c>
       <c r="G94" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>9</v>
-      </c>
-      <c r="H94" s="5" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>94</v>
       </c>
@@ -3900,13 +3341,10 @@
       </c>
       <c r="G95" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>8</v>
-      </c>
-      <c r="H95" s="5" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>95</v>
       </c>
@@ -3927,13 +3365,10 @@
       </c>
       <c r="G96" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="H96" s="5" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>96</v>
       </c>
@@ -3954,13 +3389,10 @@
       </c>
       <c r="G97" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="H97" s="5" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>97</v>
       </c>
@@ -3981,13 +3413,10 @@
       </c>
       <c r="G98" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="H98" s="5" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>98</v>
       </c>
@@ -4008,13 +3437,10 @@
       </c>
       <c r="G99" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
-      </c>
-      <c r="H99" s="5" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>99</v>
       </c>
@@ -4035,65 +3461,11 @@
       </c>
       <c r="G100" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="H100" s="5" t="s">
-        <v>309</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:H100" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <hyperlinks>
-    <hyperlink ref="H3" r:id="rId1" xr:uid="{44740A5E-F109-45C6-9A13-A4F4EAE7DA81}"/>
-    <hyperlink ref="H12" r:id="rId2" xr:uid="{5E504EC7-8957-471C-B719-01B4D83517D1}"/>
-    <hyperlink ref="H51" r:id="rId3" xr:uid="{5CC7E1F3-04A5-4009-A7F4-5ECB1A994925}"/>
-    <hyperlink ref="H52" r:id="rId4" xr:uid="{C1A25437-EB6E-40A0-B5E5-96CD29804ED2}"/>
-    <hyperlink ref="H55" r:id="rId5" xr:uid="{C82D2E6E-5B24-44A4-BB1D-BB7211C1C852}"/>
-    <hyperlink ref="H56" r:id="rId6" xr:uid="{A776E588-BCB3-42B5-9B8B-6B48E80A853A}"/>
-    <hyperlink ref="H57" r:id="rId7" xr:uid="{33844AF3-3EEE-4941-B5EF-167FF332493C}"/>
-    <hyperlink ref="H58" r:id="rId8" xr:uid="{2FD1BD28-5F5B-4289-B314-E2BB5E951180}"/>
-    <hyperlink ref="H59" r:id="rId9" xr:uid="{0CDB450D-4511-4658-9489-ABCC10CEB849}"/>
-    <hyperlink ref="H60" r:id="rId10" xr:uid="{88107DD1-E3ED-4421-BED5-3435BABCC4C4}"/>
-    <hyperlink ref="H61" r:id="rId11" xr:uid="{1A0DBDE6-E104-4A64-BB18-E4AF78B5EB84}"/>
-    <hyperlink ref="H62" r:id="rId12" xr:uid="{4932B75A-12AD-4804-BCC0-7B9EB836719E}"/>
-    <hyperlink ref="H63" r:id="rId13" xr:uid="{1C257451-3AE9-4C62-B004-979BCAF136A5}"/>
-    <hyperlink ref="H64" r:id="rId14" xr:uid="{2673EB38-A1B0-4C75-A957-F5E04BCAB107}"/>
-    <hyperlink ref="H66" r:id="rId15" xr:uid="{7093BCDF-6508-4C60-B589-52963C6F310F}"/>
-    <hyperlink ref="H67" r:id="rId16" xr:uid="{3ED3150C-C5B5-441E-B63F-40E5D95E65B2}"/>
-    <hyperlink ref="H68" r:id="rId17" xr:uid="{7B6D0D5E-7368-476A-826F-E7039336A52B}"/>
-    <hyperlink ref="H69" r:id="rId18" xr:uid="{43D3C846-AE63-481A-ABB3-847A96CC03E5}"/>
-    <hyperlink ref="H70" r:id="rId19" xr:uid="{8783941C-25FE-419E-A3E7-3DFD5F3096FE}"/>
-    <hyperlink ref="H71" r:id="rId20" xr:uid="{98860619-505F-452F-9D2B-8BCE693D3685}"/>
-    <hyperlink ref="H72" r:id="rId21" xr:uid="{A38E2513-94D0-4F9B-A4FB-D05A2D01FED9}"/>
-    <hyperlink ref="H73" r:id="rId22" xr:uid="{40C96FF8-5B4E-4AD6-8EE6-0B558951F95F}"/>
-    <hyperlink ref="H74" r:id="rId23" xr:uid="{FB7D81B4-E308-4530-A633-581C3F2A2B8A}"/>
-    <hyperlink ref="H75" r:id="rId24" xr:uid="{71FCCE82-76BF-4E43-B3CB-B1A4B928EB8C}"/>
-    <hyperlink ref="H76" r:id="rId25" xr:uid="{0D33E3C9-200F-46A0-AFA8-54FB5B2EB73B}"/>
-    <hyperlink ref="H77" r:id="rId26" xr:uid="{A989841E-1A9E-4269-94BF-15036737062B}"/>
-    <hyperlink ref="H78" r:id="rId27" xr:uid="{8CCCC026-66DF-449C-93BE-B04BD3B91F6A}"/>
-    <hyperlink ref="H79" r:id="rId28" xr:uid="{8DBA4129-2CF4-4D14-9A86-708A9F563C54}"/>
-    <hyperlink ref="H80" r:id="rId29" xr:uid="{6DF75FA9-FB4A-44D0-842E-AC1BFEDF945E}"/>
-    <hyperlink ref="H81" r:id="rId30" xr:uid="{8FF9D50D-1EBE-4B7A-B71D-DE5197A3D058}"/>
-    <hyperlink ref="H82" r:id="rId31" xr:uid="{4AF5ABF4-34B3-4D4B-A799-C1F581D732DE}"/>
-    <hyperlink ref="H83" r:id="rId32" xr:uid="{BCDAA5FF-A5EF-455D-99D7-857F9FC47BAC}"/>
-    <hyperlink ref="H84" r:id="rId33" xr:uid="{95B77834-26FC-480C-9360-A25B94900AAB}"/>
-    <hyperlink ref="H85" r:id="rId34" xr:uid="{B822F5B5-C946-49A7-A163-1BF19AEB2AD6}"/>
-    <hyperlink ref="H86" r:id="rId35" xr:uid="{0AA68751-4B4F-4D68-A717-9D61EF3D82A7}"/>
-    <hyperlink ref="H87" r:id="rId36" xr:uid="{525CB9BB-42D3-4793-B34F-F0BEC92AC036}"/>
-    <hyperlink ref="H88" r:id="rId37" xr:uid="{24256CC9-4A82-4F7B-AE2D-EBEDD37889C3}"/>
-    <hyperlink ref="H89" r:id="rId38" xr:uid="{5BF35E34-8A05-414F-96C6-BF2775729EFD}"/>
-    <hyperlink ref="H90" r:id="rId39" xr:uid="{12FEED72-670E-468E-9D4F-256CD207E865}"/>
-    <hyperlink ref="H91" r:id="rId40" xr:uid="{8301AD6B-3951-45B1-9DBA-E117868765B9}"/>
-    <hyperlink ref="H92" r:id="rId41" xr:uid="{4C219831-926F-4DE7-9B56-8D15BF54B3AA}"/>
-    <hyperlink ref="H93" r:id="rId42" xr:uid="{B7302327-1130-4B9B-8756-373DC8936B66}"/>
-    <hyperlink ref="H94" r:id="rId43" xr:uid="{BBA880CF-4CB7-4531-A2C9-F68C4D7883BA}"/>
-    <hyperlink ref="H95" r:id="rId44" xr:uid="{E355C69C-6307-4A27-8B56-F5954A79AB80}"/>
-    <hyperlink ref="H96" r:id="rId45" xr:uid="{AD5FDA0E-805E-49C9-9188-6C580E801C60}"/>
-    <hyperlink ref="H97" r:id="rId46" xr:uid="{577F2FF5-1382-452F-966A-995CAA314AC6}"/>
-    <hyperlink ref="H98" r:id="rId47" xr:uid="{353D9869-BF30-464A-BB15-AE91BB3C0ADE}"/>
-    <hyperlink ref="H99" r:id="rId48" xr:uid="{1A419798-3B9C-40CE-B1FB-78B4D81645CB}"/>
-    <hyperlink ref="H100" r:id="rId49" xr:uid="{447A01E2-C841-4209-9A93-78BAA26C2344}"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4101,57 +3473,57 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="110" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>213</v>
       </c>
